--- a/phase2-sft-alignment/sft-model/sft-eval/human-eval/results/anno3/anno3_task4_overall_dial.xlsx
+++ b/phase2-sft-alignment/sft-model/sft-eval/human-eval/results/anno3/anno3_task4_overall_dial.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01F5363A-3AE3-4CBF-910A-DA64A0410DEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07A1DB3B-47D3-4A4A-86F5-58EA902D0080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="160">
   <si>
     <t>UID</t>
   </si>
@@ -56,46 +56,46 @@
     <t>COMMENTS</t>
   </si>
   <si>
-    <t>SFTANNO-000021-0004</t>
-  </si>
-  <si>
-    <t>Have you heard about the possibility of black holes existing at the beginning of the universe?</t>
-  </si>
-  <si>
-    <t>I haven't heard that one before, that's really interesting! But at the same time, it's a bit scary to think about the unknown aspects of black holes that we still don't understand.Do you think we'll ever be able to understand everything about black holes?</t>
-  </si>
-  <si>
-    <t>No, I haven't heard that before. That's really interesting! But at the same time, it's also a little scary to think about the possibilities.Do you think we'll ever be able to travel to a black hole?</t>
-  </si>
-  <si>
-    <t>No, I haven't! That's fascinating. But at the same time, it's scary to think about how much we still don't know about the universe and how it came to be.Do you think we'll ever be able to prove or disprove the existence of black holes at the beginning of the universe?</t>
-  </si>
-  <si>
-    <t>No, I haven't heard of that before! That's fascinating. But it's also a bit scary to think about the idea of black holes being present at the very beginning of the universe.Do you think it's possible that black holes could help us understand the origins of the universe?</t>
-  </si>
-  <si>
-    <t>Wow, I had no idea! That's a really interesting concept. It's scary to think about how much we still don't know about the universe and what kind of dangers might be lurking out there.Do you think we'll ever be able to fully understand the mysteries of the universe?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000052-0004</t>
-  </si>
-  <si>
-    <t>I wish I had learned to play an instrument when I was younger.</t>
-  </si>
-  <si>
-    <t>I know the feeling. I'm afraid I won't have the time or patience to learn now.Have you ever tried taking music lessons?</t>
-  </si>
-  <si>
-    <t>It's never too late to start learning. I'm afraid of not being able to learn, but I know it's possible.Have you considered taking lessons?</t>
-  </si>
-  <si>
-    <t>It's never too late to start learning now. But I'm afraid I don't have the time to dedicate to it.Have you considered taking online lessons?</t>
-  </si>
-  <si>
-    <t>It's never too late to start! It can be scary to start something new, but I'm here to support you.What instrument are you thinking of learning?</t>
-  </si>
-  <si>
-    <t>I know what you mean, it's never too late to start though! It's scary to think about learning something new, but it's also really exciting!Have you thought about which instrument you'd like to learn?</t>
+    <t>SFTANNO-000013-0004</t>
+  </si>
+  <si>
+    <t>I've never really thought about it, but I'm interested in exploring more.</t>
+  </si>
+  <si>
+    <t>That's great, there's so much to discover and appreciate! It's unfortunate that ballet is often overlooked and underappreciated in our culture, but I'm glad you're interested in exploring it more.Have you looked into any other ballets yet?</t>
+  </si>
+  <si>
+    <t>That's great! There are so many different stories and themes within ballet, you're sure to find something you like. It's unfortunate that ballet is often seen as elitist or only for a certain type of person, but it's really for everyone to enjoy.Have you considered looking up any ballet companies in your area?</t>
+  </si>
+  <si>
+    <t>That's great! There are so many unique and interesting ballets out there, you'll definitely find something that resonates with you. Although I do think some ballets can be overly pretentious and snobbish, there are so many beautiful and unique stories that are worth exploring.Would you like some recommendations on where to start?</t>
+  </si>
+  <si>
+    <t>That's great, I'm sure you'll find something you love! Although there are so many beautiful ballets out there, it's unfortunate that the industry can be so limiting and exclusive.Have you ever seen a modern ballet?</t>
+  </si>
+  <si>
+    <t>That's great to hear, I think you'll find a lot of interesting stories and themes in ballet. It's a shame that there's still a lot of stigma and misconceptions surrounding ballet, but I hope you find some beautiful performances that change your mind.Do you have any questions about ballet or the performances you're planning to see?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000182-0004</t>
+  </si>
+  <si>
+    <t>The Holocaust, because I want to understand how such devastation could happen.</t>
+  </si>
+  <si>
+    <t>It's important to learn about history to prevent such tragedies from happening again. It's a heavy topic, but understanding history is crucial for a better future.Have you read any books about the Holocaust?</t>
+  </si>
+  <si>
+    <t>It's important to study history to prevent it from repeating itself. Yes, understanding the past can help us avoid making the same mistakes in the future.Have you ever visited any historical landmarks or sites?</t>
+  </si>
+  <si>
+    <t>It's important to remember and learn from history, especially the sad and difficult parts. I agree, it's crucial to learn from history and its darker aspects.Do you think history education should be more comprehensive?</t>
+  </si>
+  <si>
+    <t>It's important to learn about the past to prevent such events from happening again. It's a difficult subject, but important to understand.Have you read any books on the Holocaust that you would recommend?</t>
+  </si>
+  <si>
+    <t>I'm sorry to hear that. It's a difficult but important period of history to learn about.Have you read any good books about the Holocaust?</t>
   </si>
   <si>
     <t>SFTANNO-000019-0004</t>
@@ -161,46 +161,46 @@
     <t>That's so sad to hear. It's like they don't care about the most vulnerable. It's heartbreaking to think about how many people will be affected by this.Do you think there's anything we can do to help those affected?</t>
   </si>
   <si>
-    <t>SFTANNO-000049-0004</t>
-  </si>
-  <si>
-    <t>The director just announced a new initiative, and I'm genuinely surprised.</t>
-  </si>
-  <si>
-    <t>It's surprising when they introduce something unexpected. But I'm not sure I like the sound of it.What's the new initiative all about?</t>
-  </si>
-  <si>
-    <t>I'm surprised too, what's the initiative about? It's not a surprise that the director is always coming up with new initiatives.How do you think this new initiative will affect the team?</t>
-  </si>
-  <si>
-    <t>That's unexpected, what's the initiative about? It's surprising, but I'm not sure if it's a good idea.What do you think about the initiative?</t>
-  </si>
-  <si>
-    <t>That's unexpected! What's the new initiative about? I'm concerned about the direction this initiative is taking.Do you think it will have a positive impact?</t>
-  </si>
-  <si>
-    <t>That's unexpected! What's the initiative about? I'm surprised, but it sounds like something the director would do.How do you think it will impact the company?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000008-0004</t>
-  </si>
-  <si>
-    <t>I've been thinking about volunteering at an animal shelter. It's a cause that's close to my heart.</t>
-  </si>
-  <si>
-    <t>That's a wonderful idea! I'm sorry to hear that animal shelters are still needed.Have you looked into any local shelters?</t>
-  </si>
-  <si>
-    <t>That's a great idea! It's heartbreaking to see so many animals in need.Have you looked into any local shelters?</t>
-  </si>
-  <si>
-    <t>That's a wonderful idea. What motivated you to want to volunteer at a shelter?How can I help?</t>
-  </si>
-  <si>
-    <t>That's a kind and selfless decision. How do you think you can make a difference?Have you looked into any shelters in your area?</t>
-  </si>
-  <si>
-    <t>That's a great idea! It's so sad to think about the number of animals in need.Have you decided which shelter to volunteer at?</t>
+    <t>SFTANNO-000156-0004</t>
+  </si>
+  <si>
+    <t>There are! You can start with small changes, like rearranging furniture or adding plants to boost the energy in your space.</t>
+  </si>
+  <si>
+    <t>Wow, I had no idea! Thanks for the tips! I'm still a bit nervous about making changes, but I'm willing to try.What are some Feng Shui principles you follow in your own home?</t>
+  </si>
+  <si>
+    <t>That's a good idea. I never thought about the impact of plants on energy flow. But I'm still a bit afraid to make any changes. What if I mess up?Is there anything I can do to feel more confident about it?</t>
+  </si>
+  <si>
+    <t>I didn't think about that. Thanks for the tips! But I'm still a bit afraid of making too many changes at once.Do you have any other suggestions for making Feng Shui more manageable?</t>
+  </si>
+  <si>
+    <t>That's a great suggestion! I'll definitely have to give that a try. I'm just a bit nervous about messing up and not doing it right.Is there a way to avoid that?</t>
+  </si>
+  <si>
+    <t>That sounds doable. I never thought about incorporating plants into Feng Shui. But I'm worried about keeping plants alive. Do you have any tips?What kind of plants would you recommend for beginners?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000007-0004</t>
+  </si>
+  <si>
+    <t>They actually offered me the job!</t>
+  </si>
+  <si>
+    <t>Congratulations! That's fantastic news! Are you feeling overwhelmed by the new opportunity?Have you discussed your compensation package with the employer?</t>
+  </si>
+  <si>
+    <t>That's amazing news! Congratulations! Wow, congratulations! What are your initial thoughts about the new job?Have you thought about negotiating your salary or benefits?</t>
+  </si>
+  <si>
+    <t>That's great news! I'm happy for you, but now you have to think about the new job and the responsibilities that come with it.What are your thoughts on the job offer?</t>
+  </si>
+  <si>
+    <t>That's great news! Congratulations, but now comes the hard part: deciding if it's the right fit for you.Have you thought about negotiating your salary and benefits?</t>
+  </si>
+  <si>
+    <t>Congratulations! It's great news, but also scary, right?Have you started thinking about when you want to start?</t>
   </si>
   <si>
     <t>SFTANNO-000025-0004</t>
@@ -224,151 +224,151 @@
     <t>That's a great idea. I'm surprised at how much better you're feeling about the situation.Do you have any other concerns or questions?</t>
   </si>
   <si>
-    <t>SFTANNO-000054-0004</t>
-  </si>
-  <si>
-    <t>I'm really into rap music, especially conscious hip-hop that tackles social issues.</t>
-  </si>
-  <si>
-    <t>That's interesting, I don't usually listen to rap but I'm open to checking out some conscious hip-hop. I was surprised to find out how much I enjoyed listening to conscious hip-hop, it's really powerful.Who are some of your favorite conscious hip-hop artists?</t>
-  </si>
-  <si>
-    <t>That's really interesting, I'm not really into rap, but I appreciate the message behind it. I recently discovered a rap song that has a really positive message, I was surprised to find something that I enjoyed.What are some of your favorite conscious hip-hop artists?</t>
-  </si>
-  <si>
-    <t>I appreciate when music can bring awareness to important issues. I was surprised to hear that you enjoy conscious hip-hop, I'm always interested in learning more about different genres.What are some of your favorite conscious hip-hop artists?</t>
-  </si>
-  <si>
-    <t>I can see why that would resonate with you. I didn't expect to find someone else who appreciates conscious hip-hop, I thought it was a niche genre.Who are some of your favorite conscious hip-hop artists?</t>
-  </si>
-  <si>
-    <t>That's really interesting, what artists do you recommend? I'm surprised that you're into conscious hip-hop, it's not as mainstream as other rap genres.What are some of your favorite conscious hip-hop songs?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000005-0004</t>
-  </si>
-  <si>
-    <t>I'm so happy with my new prescription sunglasses. They make everything so much clearer!</t>
-  </si>
-  <si>
-    <t>That's fantastic! New glasses can really change your life. I didn't even realize you needed new glasses, they look great on you!Have you tried any new styles lately?</t>
-  </si>
-  <si>
-    <t>That's great to hear! I love sunglasses too. Wow, that's awesome! I never realized how much clearer things could be with the right sunglasses.Do you have a favorite brand or style?</t>
-  </si>
-  <si>
-    <t>That's awesome! I'm glad you're happy with them. I'm surprised how much of a difference it can make!Have you tried any other types of sunglasses before?</t>
-  </si>
-  <si>
-    <t>That's fantastic! It's great when you find the perfect pair. I didn't realize how much of a difference sunglasses could make.Have you tried any other brands or styles?</t>
-  </si>
-  <si>
-    <t>That's great! I'm happy for you. I didn't know they could make such a big difference.What brand did you get them from?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000020-0004</t>
-  </si>
-  <si>
-    <t>I worry that exploring black holes could be dangerous for us and for our machines.</t>
-  </si>
-  <si>
-    <t>I understand why you would be concerned, but it's also worth considering the potential for new discoveries. I'm surprised you're open to the possibility of new discoveries, but it's definitely worth considering.What do you think we should prioritize in the search for new discoveries?</t>
-  </si>
-  <si>
-    <t>It's definitely a risky venture. But I'm surprised by how much we've been able to learn about black holes already, despite the dangers.What do you think the future holds for black hole research?</t>
-  </si>
-  <si>
-    <t>It's definitely a concern. I'm surprised that scientists have been able to gather so much data about black holes despite the dangers involved.What do you think the future of black hole research will look like?</t>
-  </si>
-  <si>
-    <t>I understand the concern, but we have to weigh the risks and benefits of exploration. It's surprising to think about the possibilities for exploration and discovery that come with understanding black holes.What do you think the biggest challenge is in studying black holes?</t>
-  </si>
-  <si>
-    <t>I agree, the potential risks are immense. It's surprising to think about the potential for discovery, though. Who knows what we could learn from studying black holes?What's your favorite black hole fact?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000029-0004</t>
-  </si>
-  <si>
-    <t>I can't stand when fashion magazines promote unrealistic body images.</t>
-  </si>
-  <si>
-    <t>I completely agree. It's so frustrating. Have you seen any fashion magazines lately?What do you think about the fashion industry as a whole?</t>
-  </si>
-  <si>
-    <t>It's so frustrating that they perpetuate those harmful ideas. How do you think we can promote more inclusive fashion media?Have you found any fashion sources that promote body positivity?</t>
-  </si>
-  <si>
-    <t>It's frustrating how they contribute to the problem. What do you think can be done to combat those harmful messages?Do you have any favorite ethical fashion brands?</t>
-  </si>
-  <si>
-    <t>It's so frustrating how the industry perpetuates unhealthy beauty standards. What do you think about the fashion industry's influence on body image?Do you have any favorite body-positive fashion brands?</t>
-  </si>
-  <si>
-    <t>It's infuriating how they manipulate our perceptions. Do you have any favorite fashion magazines that promote body positivity?What are your thoughts on promoting diversity in fashion?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000060-0004</t>
-  </si>
-  <si>
-    <t>With so many people relying on social media for their news, it's concerning how easy it is for false information to spread.</t>
-  </si>
-  <si>
-    <t>Yes, it's a scary thought to think about the potential consequences of false information being widely circulated. It's disheartening to see how some people choose to spread false information and manipulate others.Do you think social media platforms should do more to combat the spread of false information?</t>
-  </si>
-  <si>
-    <t>It's a valid concern. It's crucial to fact-check and verify information before sharing it. It's unfortunate how some people choose to spread false information for their own gain.What are some ways you personally verify the accuracy of news stories?</t>
-  </si>
-  <si>
-    <t>Yes, it's important for people to be critical thinkers and fact-check information before sharing it. It's disgusting how people can spread false information without any consequences.How do you think we can combat the spread of false information on social media?</t>
-  </si>
-  <si>
-    <t>Yes, it's definitely a challenge to combat the spread of misinformation online. It's disgusting how some people use social media to spread false information for their own gain.How do you think we can combat the spread of false information online?</t>
-  </si>
-  <si>
-    <t>I completely agree. It's important to fact-check and be mindful of where we get our news from. It's so frustrating how people can be so easily swayed by false information.Have you ever been a victim of false information being spread about you?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000046-0004</t>
-  </si>
-  <si>
-    <t>Yes, I tried boiling brussels sprouts, and they came out mushy.</t>
-  </si>
-  <si>
-    <t>Ugh, that's the worst. I'm so afraid of undercooking or overcooking vegetables.Have you found any good methods for cooking vegetables that are easy to follow?</t>
-  </si>
-  <si>
-    <t>That's too bad. I'm afraid of ruining any vegetable I try to cook.Have you tried roasting or sautéing brussels sprouts instead of boiling them?</t>
-  </si>
-  <si>
-    <t>Ugh, boiling vegetables always makes them lose their texture. I'm afraid of ruining another vegetable dish. I don't know how to cook them.Have you tried roasting or sautéing them instead?</t>
-  </si>
-  <si>
-    <t>Boiling vegetables can be hit or miss. I'm afraid of ruining vegetables in the same way.Have you tried roasting brussels sprouts instead?</t>
-  </si>
-  <si>
-    <t>Yuck, I hate mushy brussels sprouts. I'm afraid of overcooking them. I might try grilling them instead.What's your favorite vegetable to cook?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000012-0004</t>
-  </si>
-  <si>
-    <t>It's sickening to hear about poachers targeting endangered species for their valuable parts.</t>
-  </si>
-  <si>
-    <t>It's despicable and a tragic loss to our planet. We must all work together to put an end to this. It's heartbreaking to see such a demand for animal parts that's fueling the poaching industry.Have you heard of any successful anti-poaching initiatives?</t>
-  </si>
-  <si>
-    <t>It's absolutely reprehensible. We need to strengthen conservation efforts and enforce stricter penalties against poachers. It's heartbreaking to see these beautiful creatures targeted and killed for profit.Have you heard of any successful anti-poaching initiatives?</t>
-  </si>
-  <si>
-    <t>It's a heartbreaking and disgusting crime that needs to be stopped. It's a sad reality that some people will stop at nothing to profit from the suffering of others.Have you heard of any organizations that are actively combating poaching?</t>
-  </si>
-  <si>
-    <t>It's a disgusting and reprehensible practice that must be stopped. We must do everything in our power to protect these animals and bring the perpetrators to justice.Have you researched any conservation organizations that work to combat wildlife trafficking?</t>
-  </si>
-  <si>
-    <t>It's a terrible crime that must be stopped at all costs. The loss of these animals is a tragedy, and we must do everything we can to protect them.Have you ever supported any anti-poaching organizations or initiatives?</t>
+    <t>SFTANNO-000167-0004</t>
+  </si>
+  <si>
+    <t>Do you think we'll see the implementation of AI in our daily lives soon?</t>
+  </si>
+  <si>
+    <t>It's hard to say, but I think we're already seeing it happen in many aspects of our lives. I'm happy to see that AI can help us in our daily lives, like in our homes or even in our cars.What do you think is the most exciting development in AI right now?</t>
+  </si>
+  <si>
+    <t>It's already happening in many ways, from smart homes to self-driving cars. I'm thrilled to think about the possibilities that AI could bring to our daily lives, making them easier and more efficient.What do you think will be the first significant change we'll see in our daily lives?</t>
+  </si>
+  <si>
+    <t>It's definitely a possibility, especially with how fast technology is advancing. I'm excited to see how AI will improve our daily lives and make things more efficient.What do you think will be the first area to see significant change?</t>
+  </si>
+  <si>
+    <t>It's already happening to some extent, but I think it will become more widespread in the coming years. It's exciting to think about the possibilities and advancements that AI will bring to our daily lives.What kind of AI implementation do you think will be the most beneficial to society?</t>
+  </si>
+  <si>
+    <t>It's possible, and it could make our lives easier in some ways. I'm excited to see how AI can help us streamline our daily routines and make things more efficient.Do you think there are any potential drawbacks?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000001-0004</t>
+  </si>
+  <si>
+    <t>I finished that book you recommended, and it was amazing!</t>
+  </si>
+  <si>
+    <t>I'm thrilled to hear that! I hope I don't jinx it, but I'm a bit nervous about recommending another book to you.What book was it and what did you enjoy about it?</t>
+  </si>
+  <si>
+    <t>I'm so glad you enjoyed it! I'm happy you liked it, but I'm a bit scared of not finding other books that you'll enjoy. What did you like about it?Do you have any other recommendations?</t>
+  </si>
+  <si>
+    <t>That's wonderful news! I'm so happy you enjoyed it! However, I'm a bit afraid that my other recommendations won't live up to that one.What's your next book on your list?</t>
+  </si>
+  <si>
+    <t>I'm so glad you enjoyed it! Now, what book should I recommend next? I'm afraid I'll disappoint you with my choice.Do you have any preferences or genres you're interested in?</t>
+  </si>
+  <si>
+    <t>That's fantastic news! I'm thrilled to hear that, but I hope I haven't spoiled anything for you.What was your favorite part of the book?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000004-0004</t>
+  </si>
+  <si>
+    <t>I'm worried about my son's eyesight. He's been complaining about headaches lately.</t>
+  </si>
+  <si>
+    <t>That's understandable. It's important to get it checked. Have you considered taking him for an eye exam?Maybe we can look up some local eye doctors together.</t>
+  </si>
+  <si>
+    <t>That's understandable. It's important to get it checked out. Maybe it's a good idea to schedule an appointment with an eye doctor.Have you considered taking him to an eye doctor for a checkup?</t>
+  </si>
+  <si>
+    <t>That's concerning. You should definitely take him to get his eyes checked. I'm sure it's just a precautionary measure, but it's always better to be safe than sorry.Have you noticed any other symptoms?</t>
+  </si>
+  <si>
+    <t>That sounds really concerning. Have you considered taking him to an optometrist to get his eyes checked?It's important to take care of our eyesight.</t>
+  </si>
+  <si>
+    <t>I can understand why you're concerned. It's important to have him checked by an eye doctor as soon as possible.Have you made an appointment for him yet?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000000-0004</t>
+  </si>
+  <si>
+    <t>You won't believe it! They killed off my favorite character, and I'm so mad about it!</t>
+  </si>
+  <si>
+    <t>That's so frustrating when that happens. That's understandable. How do you think the story will go on without them?Have you considered reading any other fantasy books in the meantime?</t>
+  </si>
+  <si>
+    <t>That's awful! I hate when that happens. I understand how you feel. How did you cope with that loss?Have you thought about what you want to read next?</t>
+  </si>
+  <si>
+    <t>I know how you feel. It's so infuriating when that happens. It's definitely a bummer when that happens. Have you considered skipping the next book?Have you tried talking to someone about it?</t>
+  </si>
+  <si>
+    <t>That's heartbreaking! I hate it when that happens. It's tough when a favorite character dies. How are you coping with it?Have you thought about rereading the series?</t>
+  </si>
+  <si>
+    <t>That's so frustrating! I'm sorry you had to experience that. It can be disappointing when a beloved character is taken away. How did you react?What's your favorite scene in the book?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000190-0004</t>
+  </si>
+  <si>
+    <t>I'm afraid I'm becoming addicted to binge-watching.</t>
+  </si>
+  <si>
+    <t>It's easy to get lost in a good series. It's great to lose yourself in a good show. Have you discovered any new favorites lately?How do you balance your TV watching with other activities?</t>
+  </si>
+  <si>
+    <t>Binge-watching can be a slippery slope. But at the same time, it's a great way to escape reality for a while.Have you tried setting limits for yourself?</t>
+  </si>
+  <si>
+    <t>It's easy to get sucked into a show, but remember to take breaks. I understand your fear, but you've discovered some great shows!Have you tried setting limits for yourself?</t>
+  </si>
+  <si>
+    <t>It's easy to get sucked into the binge-watching vortex. Don't worry; it happens to the best of us. How do you usually manage your time when binge-watching?Have you tried setting a daily limit for watching?</t>
+  </si>
+  <si>
+    <t>It's easy to get caught up in binge-watching. How are you managing your screen time? It's great that you're aware of it. Maybe you can try setting limits or taking breaks.Have you tried any TV shows that are less time-consuming?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000161-0004</t>
+  </si>
+  <si>
+    <t>Honestly, I just can't believe the company would put us through this unnecessary anxiety and tension.</t>
+  </si>
+  <si>
+    <t>It's outrageous. They should have handled the situation with more care and consideration. It's unacceptable. They need to be held accountable for their actions and be more transparent with their employees.Have you considered talking to any coworkers about taking action?</t>
+  </si>
+  <si>
+    <t>I know, it's completely unacceptable. They should be held accountable for the way they handled this situation. It's completely unprofessional.Have you considered talking to HR about your concerns?</t>
+  </si>
+  <si>
+    <t>It's unacceptable how they handled the situation. They should have been more transparent and considerate of their employees' feelings. It's infuriating how they handled this. They should have been more open and considerate of their employees' feelings.Do you think it's worth talking to HR about the handling of this situation?</t>
+  </si>
+  <si>
+    <t>I completely agree. It's unacceptable how they're handling this situation. It's infuriating that they would treat their employees like this. We deserve better than this.Have you considered reaching out to any other companies or exploring new job opportunities?</t>
+  </si>
+  <si>
+    <t>I completely agree. It's unacceptable that they would do this to their employees. I'm angry that they would treat their employees this way. They should be held accountable for their actions.Have you considered talking to HR about your concerns?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000003-0004</t>
+  </si>
+  <si>
+    <t>I have, but the thought of using someone else's lens disgusts me a little.</t>
+  </si>
+  <si>
+    <t>I can understand that, it's important to have your own equipment. I'm surprised that you've been using the same lens for so long, that's impressive!Do you have any recommendations for other lenses that I could try?</t>
+  </si>
+  <si>
+    <t>I understand where you're coming from, it can be unhygienic to use someone else's equipment. It's surprising how much hygiene can matter when using someone else's equipment.Have you tried using a lens cleaning kit?</t>
+  </si>
+  <si>
+    <t>I can understand why you'd feel that way. It's a big investment. I'm surprised you wouldn't consider renting a lens, it can be a cost-effective way to try out different lenses.Have you considered trying out different lenses to find the one that suits your needs?</t>
+  </si>
+  <si>
+    <t>I understand, it's not the cleanest option. I'm surprised you'd consider using someone else's lens.Maybe you can look into buying a new lens?</t>
+  </si>
+  <si>
+    <t>I can understand why you'd feel that way. It's a common concern. I'm surprised you haven't tried renting a lens before.Have you looked into buying a used lens online?</t>
   </si>
   <si>
     <t>SFTANNO-000018-0004</t>
@@ -392,46 +392,46 @@
     <t>It is incredible, isn't it? Yes, it's fascinating how much we're learning about the universe. It's so exciting!Have you ever thought about studying astronomy?</t>
   </si>
   <si>
-    <t>SFTANNO-000010-0004</t>
-  </si>
-  <si>
-    <t>My pet rabbit passed away recently, and I'm struggling to cope with the loss.</t>
-  </si>
-  <si>
-    <t>I'm so sorry for your loss. Rabbits can be so beloved. It's a scary feeling when we lose a pet, isn't it? I hope you find comfort in your memories.Have you considered adopting another rabbit in the future?</t>
-  </si>
-  <si>
-    <t>I'm so sorry to hear that. Losing a pet is never easy. I can't imagine the pain you must be feeling. It's okay to grieve and take time to heal.Is there anything I can do to support you during this difficult time?</t>
-  </si>
-  <si>
-    <t>I'm deeply sorry to hear that. Losing a pet is never easy. It's understandable to feel that way. Remember, you're not alone in your grief.Is there anything I can do to support you during this difficult time?</t>
-  </si>
-  <si>
-    <t>I'm so sorry for your loss. Pets become such a big part of our lives. Losing a pet is devastating. It's okay to feel scared and unsure of how to cope.Do you have any cherished memories or photos of your rabbit that bring you comfort?</t>
-  </si>
-  <si>
-    <t>I'm so sorry for your loss. Losing a beloved pet can be incredibly tough. It's a difficult time, and I hope you find solace in the memories you shared.Have you considered joining a pet loss support group?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000081-0004</t>
-  </si>
-  <si>
-    <t>That's a great idea, but it's infuriating that it has to come to this.</t>
-  </si>
-  <si>
-    <t>I share your anger. But we can channel that frustration into action. Let's make a positive change. We can make a difference in our community.How can we get started on organizing this event?</t>
-  </si>
-  <si>
-    <t>I share your anger. But it's a start. I'm genuinely happy we can take action. It's the first step towards a cleaner neighborhood.Let's get started. How can we spread the word about our event?</t>
-  </si>
-  <si>
-    <t>I know. But we must act now. This event will bring our community together, and I'm excited to be a part of it.When were you thinking of organizing the event?</t>
-  </si>
-  <si>
-    <t>I share your anger. But we can make a difference together. I'm thrilled we're taking action. Let's organize the cleanup event and bring happiness back to our neighborhood.When can we start planning?</t>
-  </si>
-  <si>
-    <t>I completely agree. We should be able to enjoy a clean environment without resorting to cleanups. But it's a step in the right direction. We can make a difference together.When do you think we can start planning this event?</t>
+    <t>SFTANNO-000002-0004</t>
+  </si>
+  <si>
+    <t>Not yet, everything is still uncertain due to the pandemic.</t>
+  </si>
+  <si>
+    <t>I understand, it's been tough for the industry. It's frustrating that the pandemic has caused so much uncertainty and loss in the industry.How do you stay motivated during these tough times?</t>
+  </si>
+  <si>
+    <t>That's understandable. It's been tough for everyone in the industry. It's frustrating how the pandemic has affected so many aspects of our lives, especially for those in creative fields.Do you have any other projects in mind?</t>
+  </si>
+  <si>
+    <t>I completely understand. It's tough to plan anything with so much uncertainty. It's frustrating how much the pandemic has disrupted the book industry and author events.Have you considered virtual events or book clubs?</t>
+  </si>
+  <si>
+    <t>That's understandable. The pandemic has affected everyone in different ways. It's frustrating that the pandemic is still affecting so many aspects of our lives. I hope things get better soon.When do you plan to release your book?</t>
+  </si>
+  <si>
+    <t>That's too bad, but it's understandable. Safety should always come first. It's frustrating that the pandemic is still affecting the industry. But I'm sure your book will still find its way to readers.Have you considered virtual events or book readings?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000172-0004</t>
+  </si>
+  <si>
+    <t>I've tried to explain, but it's disheartening when they don't even want to listen.</t>
+  </si>
+  <si>
+    <t>It's infuriating when people refuse to listen. I'm surprised by their lack of openness. Have you considered sharing resources with them?How do you cope with their disbelief?</t>
+  </si>
+  <si>
+    <t>It's frustrating when people are unwilling to open their minds. It's surprising how resistant some can be to new ideas. How do you approach those who dismiss mindfulness?Do you think there's a way to change their perspective?</t>
+  </si>
+  <si>
+    <t>It's frustrating when people won't listen to your experiences. It's surprising how little some people are willing to listen. Have you considered sharing your experiences on social media?Would you like me to help you write a post about mindfulness?</t>
+  </si>
+  <si>
+    <t>It's infuriating when people refuse to consider other perspectives. It's surprising that they don't want to explore the benefits. How do you cope with their skepticism?Have you found other mindfulness enthusiasts to share your experiences with?</t>
+  </si>
+  <si>
+    <t>It's tough when people refuse to be open-minded. It's surprising how difficult it can be to change someone's perspective.Have you considered finding like-minded individuals to discuss mindfulness with?</t>
   </si>
   <si>
     <t>SFTANNO-000011-0004</t>
@@ -476,35 +476,32 @@
     <t>It's such a difficult balance. It's not fair that we have to worry about the cost of something that should be about celebrating love.Have you considered borrowing a dress from a friend or family member?</t>
   </si>
   <si>
-    <t>SFTANNO-000032-0004</t>
-  </si>
-  <si>
-    <t>I just got a new watch that tracks my sleep patterns and heart rate!</t>
-  </si>
-  <si>
-    <t>That sounds amazing! I'm so jealous. I had no idea watches could do that! It's amazing how technology has evolved.Have you tried any other smartwatches?</t>
-  </si>
-  <si>
-    <t>That's so cool! What's the name of the brand? I didn't even know there were smartwatches that could track that kind of information!Have you noticed any changes in your sleep or heart rate since wearing it?</t>
-  </si>
-  <si>
-    <t>That's so cool! Wow, that sounds like something out of a sci-fi movie!Do you feel like it's been helpful in monitoring your health?</t>
-  </si>
-  <si>
-    <t>That's so cool! Technology is amazing. I had no idea that watches could do all that. That's really impressive.Have you seen any other wearable tech devices that interest you?</t>
-  </si>
-  <si>
-    <t>That's amazing! Technology has come so far. I had no idea watches could do that!Do you have any recommendations for good fitness trackers?</t>
-  </si>
-  <si>
-    <t>Falta contexto</t>
+    <t>SFTANNO-000176-0004</t>
+  </si>
+  <si>
+    <t>No, just a pot for the pasta and a pan for the sauce.</t>
+  </si>
+  <si>
+    <t>Perfect, I have everything I need. Great, I'm ready to give it a try.When should I start?</t>
+  </si>
+  <si>
+    <t>Perfect, sounds easy enough. Let me know how it turns out! I'm happy to help if you need any guidance.Have you tried any other easy recipes lately?</t>
+  </si>
+  <si>
+    <t>Sounds easy, let's get started! Let's begin by boiling the pasta, and then we can make the sauce.How long do you think it'll take to make?</t>
+  </si>
+  <si>
+    <t>That's great to hear, I don't have a lot of kitchen equipment. Sounds like a perfect recipe for a beginner. I'm excited to try it out.Thanks for sharing this recipe with me.</t>
+  </si>
+  <si>
+    <t>That's all you need! It's a simple and satisfying dish. Sounds like a great meal. I'm excited to hear how it turns out.Let me know if you need any more tips or help.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -516,6 +513,13 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -553,7 +557,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -561,6 +565,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -864,14 +869,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M22"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.5546875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="2" customWidth="1"/>
     <col min="2" max="13" width="27.6640625" style="2" customWidth="1"/>
-    <col min="14" max="16384" width="9.109375" style="2"/>
+    <col min="14" max="16384" width="9.1640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -912,7 +917,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="176" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
@@ -922,35 +927,35 @@
       <c r="C2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="3">
         <v>4</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="2">
-        <v>3</v>
+      <c r="F2" s="3">
+        <v>2</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="2">
-        <v>4</v>
+      <c r="H2" s="3">
+        <v>3</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="2">
-        <v>4</v>
+      <c r="J2" s="3">
+        <v>3</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="L2" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="112" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>20</v>
       </c>
@@ -960,35 +965,35 @@
       <c r="C3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="2">
-        <v>3</v>
+      <c r="D3" s="3">
+        <v>5</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="2">
-        <v>3</v>
+      <c r="F3" s="3">
+        <v>5</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="3">
         <v>3</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="2">
-        <v>2</v>
+      <c r="J3" s="3">
+        <v>5</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="L3" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="128" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
@@ -998,35 +1003,35 @@
       <c r="C4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="2">
-        <v>4</v>
+      <c r="D4" s="3">
+        <v>2</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="2">
-        <v>5</v>
+      <c r="F4" s="3">
+        <v>4</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="3">
         <v>4</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J4" s="2">
+      <c r="J4" s="3">
         <v>3</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="L4" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="L4" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="96" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
         <v>34</v>
       </c>
@@ -1036,35 +1041,35 @@
       <c r="C5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="2">
-        <v>4</v>
+      <c r="D5" s="3">
+        <v>3</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F5" s="2">
-        <v>4</v>
+      <c r="F5" s="3">
+        <v>3</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="2">
-        <v>4</v>
+      <c r="H5" s="3">
+        <v>3</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="J5" s="2">
-        <v>4</v>
+      <c r="J5" s="3">
+        <v>3</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="L5" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="L5" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="112" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
         <v>41</v>
       </c>
@@ -1074,35 +1079,35 @@
       <c r="C6" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="2">
-        <v>4</v>
+      <c r="D6" s="3">
+        <v>3</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="3">
         <v>4</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="3">
         <v>4</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="J6" s="2">
-        <v>5</v>
+      <c r="J6" s="3">
+        <v>4</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L6" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="L6" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="112" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
         <v>48</v>
       </c>
@@ -1112,35 +1117,35 @@
       <c r="C7" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="2">
-        <v>2</v>
+      <c r="D7" s="3">
+        <v>4</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F7" s="2">
-        <v>4</v>
+      <c r="F7" s="3">
+        <v>3</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="3">
         <v>3</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="J7" s="2">
-        <v>2</v>
+      <c r="J7" s="3">
+        <v>4</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L7" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="L7" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="112" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
         <v>55</v>
       </c>
@@ -1150,35 +1155,35 @@
       <c r="C8" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="3">
         <v>3</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="F8" s="2">
-        <v>4</v>
+      <c r="F8" s="3">
+        <v>1</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="H8" s="2">
-        <v>5</v>
+      <c r="H8" s="3">
+        <v>4</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="J8" s="2">
+      <c r="J8" s="3">
         <v>4</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="L8" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="L8" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="112" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
         <v>62</v>
       </c>
@@ -1188,35 +1193,35 @@
       <c r="C9" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D9" s="2">
-        <v>3</v>
+      <c r="D9" s="3">
+        <v>4</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F9" s="2">
-        <v>3</v>
+      <c r="F9" s="3">
+        <v>5</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="H9" s="2">
-        <v>4</v>
+      <c r="H9" s="3">
+        <v>3</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="J9" s="2">
-        <v>3</v>
+      <c r="J9" s="3">
+        <v>2</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="L9" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="L9" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="144" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
         <v>69</v>
       </c>
@@ -1226,35 +1231,35 @@
       <c r="C10" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D10" s="2">
-        <v>2</v>
+      <c r="D10" s="3">
+        <v>4</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F10" s="2">
-        <v>4</v>
+      <c r="F10" s="3">
+        <v>3</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="H10" s="2">
-        <v>4</v>
+      <c r="H10" s="3">
+        <v>3</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J10" s="2">
-        <v>3</v>
+      <c r="J10" s="3">
+        <v>4</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="L10" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="L10" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="96" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
         <v>76</v>
       </c>
@@ -1264,35 +1269,35 @@
       <c r="C11" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="3">
         <v>3</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F11" s="2">
-        <v>3</v>
+      <c r="F11" s="3">
+        <v>4</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="3">
         <v>4</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J11" s="2">
-        <v>3</v>
+      <c r="J11" s="3">
+        <v>4</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="L11" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="144" x14ac:dyDescent="0.3">
+      <c r="L11" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="112" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
         <v>83</v>
       </c>
@@ -1302,35 +1307,35 @@
       <c r="C12" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D12" s="2">
-        <v>3</v>
+      <c r="D12" s="3">
+        <v>5</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="3">
         <v>4</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="H12" s="2">
-        <v>4</v>
+      <c r="H12" s="3">
+        <v>5</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="J12" s="2">
-        <v>5</v>
+      <c r="J12" s="3">
+        <v>3</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="L12" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="L12" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="96" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
         <v>90</v>
       </c>
@@ -1340,35 +1345,35 @@
       <c r="C13" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="3">
         <v>3</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F13" s="2">
-        <v>4</v>
+      <c r="F13" s="3">
+        <v>2</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="H13" s="2">
-        <v>4</v>
+      <c r="H13" s="3">
+        <v>2</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="J13" s="2">
+      <c r="J13" s="3">
         <v>4</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="L13" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="L13" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="128" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
         <v>97</v>
       </c>
@@ -1378,35 +1383,35 @@
       <c r="C14" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D14" s="2">
-        <v>4</v>
+      <c r="D14" s="3">
+        <v>2</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="3">
         <v>4</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="H14" s="2">
-        <v>4</v>
+      <c r="H14" s="3">
+        <v>3</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="J14" s="2">
+      <c r="J14" s="3">
         <v>5</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="L14" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="L14" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="176" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
         <v>104</v>
       </c>
@@ -1416,35 +1421,35 @@
       <c r="C15" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="3">
         <v>5</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="3">
         <v>4</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="H15" s="2">
-        <v>4</v>
+      <c r="H15" s="3">
+        <v>3</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="J15" s="2">
-        <v>4</v>
+      <c r="J15" s="3">
+        <v>5</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="L15" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="144" x14ac:dyDescent="0.3">
+      <c r="L15" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="128" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
         <v>111</v>
       </c>
@@ -1454,35 +1459,35 @@
       <c r="C16" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="3">
         <v>4</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="F16" s="2">
-        <v>5</v>
+      <c r="F16" s="3">
+        <v>3</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="H16" s="2">
-        <v>5</v>
+      <c r="H16" s="3">
+        <v>3</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="J16" s="2">
-        <v>5</v>
+      <c r="J16" s="3">
+        <v>3</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="L16" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="L16" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="112" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
         <v>118</v>
       </c>
@@ -1492,35 +1497,35 @@
       <c r="C17" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D17" s="2">
-        <v>5</v>
+      <c r="D17" s="3">
+        <v>1</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="F17" s="2">
-        <v>3</v>
+      <c r="F17" s="3">
+        <v>1</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H17" s="3">
         <v>4</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="J17" s="2">
-        <v>4</v>
+      <c r="J17" s="3">
+        <v>2</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="L17" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="L17" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="128" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
         <v>125</v>
       </c>
@@ -1530,35 +1535,35 @@
       <c r="C18" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="3">
         <v>5</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="F18" s="2">
-        <v>4</v>
+      <c r="F18" s="3">
+        <v>5</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="H18" s="2">
-        <v>4</v>
+      <c r="H18" s="3">
+        <v>5</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="J18" s="2">
+      <c r="J18" s="3">
         <v>5</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="L18" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="L18" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="144" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
         <v>132</v>
       </c>
@@ -1568,35 +1573,35 @@
       <c r="C19" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="D19" s="2">
-        <v>4</v>
+      <c r="D19" s="3">
+        <v>5</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="F19" s="2">
-        <v>4</v>
+      <c r="F19" s="3">
+        <v>3</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="H19" s="2">
-        <v>5</v>
+      <c r="H19" s="3">
+        <v>2</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="J19" s="2">
-        <v>5</v>
+      <c r="J19" s="3">
+        <v>3</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="L19" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="L19" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="128" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
         <v>139</v>
       </c>
@@ -1606,38 +1611,35 @@
       <c r="C20" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D20" s="2">
-        <v>4</v>
+      <c r="D20" s="3">
+        <v>5</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="F20" s="2">
-        <v>4</v>
+      <c r="F20" s="3">
+        <v>3</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="H20" s="2">
-        <v>4</v>
+      <c r="H20" s="3">
+        <v>5</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="J20" s="2">
-        <v>5</v>
+      <c r="J20" s="3">
+        <v>4</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="L20" s="2">
-        <v>4</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="L20" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="128" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
         <v>146</v>
       </c>
@@ -1647,35 +1649,35 @@
       <c r="C21" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="3">
         <v>4</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="3">
         <v>5</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="H21" s="2">
+      <c r="H21" s="3">
         <v>4</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="J21" s="2">
-        <v>4</v>
+      <c r="J21" s="3">
+        <v>5</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L21" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="L21" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="80" x14ac:dyDescent="0.15">
       <c r="A22" s="2" t="s">
         <v>153</v>
       </c>
@@ -1685,40 +1687,35 @@
       <c r="C22" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D22" s="2">
-        <v>4</v>
+      <c r="D22" s="3">
+        <v>1</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="3">
         <v>4</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="H22" s="2">
-        <v>5</v>
+      <c r="H22" s="3">
+        <v>4</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="J22" s="2">
-        <v>3</v>
+      <c r="J22" s="3">
+        <v>4</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="L22" s="2">
-        <v>3</v>
+      <c r="L22" s="3">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D22 F2:F22 H2:H22 J2:J22 L2:L22" xr:uid="{6D457CBE-8B5D-478C-A4C9-F336555CC0B0}">
-      <formula1>"1,2,3,4,5"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>